--- a/Result/02-14-26/HKEXstock_02-14-26period252RS80.xlsx
+++ b/Result/02-14-26/HKEXstock_02-14-26period252RS80.xlsx
@@ -2639,7 +2639,7 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="AC22" s="2" t="inlineStr">
+      <c r="AC22" s="3" t="inlineStr">
         <is>
           <t>Communication Services</t>
         </is>
